--- a/physics/first_term/labs/lab5/calc.xlsx
+++ b/physics/first_term/labs/lab5/calc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miwm64/itmo/practice/itmo_cse/physics/first_term/labs/lab5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591B0F32-2911-A546-9282-509F0496903D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2254281-263C-3043-9A4F-5D6932E55D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{ADA14C3B-06AC-2448-8A50-5C48B52BBF76}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{ADA14C3B-06AC-2448-8A50-5C48B52BBF76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
